--- a/StructureDefinition-openelis-order-task.xlsx
+++ b/StructureDefinition-openelis-order-task.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T02:24:20+00:00</t>
+    <t>2026-10-12T15:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -895,7 +895,7 @@
     <t>The current status of the task.</t>
   </si>
   <si>
-    <t>Entered = ready. Started or technical acceptance = in-progress. Technical rejection = failed. Non-conforming or biologist rejected = rejected. Finished = completed.</t>
+    <t>A cancelled order = cancelled. Entered = ready. Started or technical acceptance = in-progress. Technical rejection = failed. Non-conforming, biologist rejected or sample rejected = rejected. Sample cancelled = cancelled. Finished = completed. Any other status = in-progress.</t>
   </si>
   <si>
     <t>These states enable coordination of task status with off-the-shelf workflow solutions that support automation of tasks.</t>
@@ -1615,7 +1615,7 @@
     <t>The name of the Output parameter.</t>
   </si>
   <si>
-    <t>Currently a bare code 'reference' with no system.</t>
+    <t>{base}/task_output#DiagnosticReport, as on referral Tasks.</t>
   </si>
   <si>
     <t>Outputs are named to enable task automation to bind data and pass it from one task to the next.</t>
@@ -1679,6 +1679,9 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://openelis-global.org/task_output</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -1721,7 +1724,7 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>reference</t>
+    <t>DiagnosticReport</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -11492,7 +11495,7 @@
         <v>79</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>79</v>
+        <v>537</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>79</v>
@@ -11531,7 +11534,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11552,21 +11555,21 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11592,13 +11595,13 @@
         <v>164</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11648,7 +11651,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11669,21 +11672,21 @@
         <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11709,14 +11712,14 @@
         <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -11726,7 +11729,7 @@
         <v>79</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>79</v>
@@ -11765,7 +11768,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11786,21 +11789,21 @@
         <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11826,14 +11829,14 @@
         <v>164</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -11882,7 +11885,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -11903,21 +11906,21 @@
         <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11940,19 +11943,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12001,7 +12004,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12022,21 +12025,21 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12062,16 +12065,16 @@
         <v>164</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -12120,7 +12123,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12141,21 +12144,21 @@
         <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12178,17 +12181,17 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12237,7 +12240,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>90</v>

--- a/StructureDefinition-openelis-order-task.xlsx
+++ b/StructureDefinition-openelis-order-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:07:11+00:00</t>
+    <t>2026-10-12T15:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-order-task.xlsx
+++ b/StructureDefinition-openelis-order-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:22:52+00:00</t>
+    <t>2026-10-14T21:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
